--- a/Budget/data/budget_2022.xlsx
+++ b/Budget/data/budget_2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59A7BFE7-07CA-4A96-B7BD-A689F4709338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDDB7CA-F5CD-4F5A-BD83-BB4246DDA57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AA9ED6E-368D-482D-9C64-CEA0551C5F34}"/>
   </bookViews>
@@ -519,8 +519,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F514F26-19E1-4C5D-B90E-ADD6D49F7504}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/Budget/data/budget_2022.xlsx
+++ b/Budget/data/budget_2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDDB7CA-F5CD-4F5A-BD83-BB4246DDA57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB9B1E2-EDF4-409D-B4BD-4949428C89F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AA9ED6E-368D-482D-9C64-CEA0551C5F34}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Ministry</t>
   </si>
@@ -87,24 +87,12 @@
     <t>Judicial Service Commission</t>
   </si>
   <si>
-    <t>Anambra State Internal Revenue Service</t>
-  </si>
-  <si>
     <t>Ministry of Information</t>
   </si>
   <si>
     <t>Office of the Head of Service</t>
   </si>
   <si>
-    <t>Anambra State Investment Promotion &amp; Protection Agency</t>
-  </si>
-  <si>
-    <t>Christian Pilgrims Welfare Board</t>
-  </si>
-  <si>
-    <t>Muslim Pilgrims Welfare Board</t>
-  </si>
-  <si>
     <t>Ministry of Homeland Affairs</t>
   </si>
   <si>
@@ -136,12 +124,30 @@
   </si>
   <si>
     <t>Ministry of Lands</t>
+  </si>
+  <si>
+    <t>Office of the Auditor General (State)</t>
+  </si>
+  <si>
+    <t>Civil Service Commission</t>
+  </si>
+  <si>
+    <t>Local Government Civil Service Commission</t>
+  </si>
+  <si>
+    <t>Awka Capital Teritory Development Authority - ACTDA</t>
+  </si>
+  <si>
+    <t>Ministry of Tertiary and Science Education</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₦&quot;#,##0.00;[Red]\-&quot;₦&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -151,9 +157,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -192,15 +198,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -517,15 +520,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F514F26-19E1-4C5D-B90E-ADD6D49F7504}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,628 +542,648 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>643829526.5</v>
-      </c>
-      <c r="C2" s="3">
-        <v>28607825825</v>
-      </c>
-      <c r="D2" s="3">
-        <v>36643366813</v>
-      </c>
-      <c r="E2" s="3">
-        <v>9000000000</v>
-      </c>
-      <c r="F2" s="3">
-        <v>45643366813</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>4080308483</v>
+      </c>
+      <c r="C2" s="2">
+        <v>16804756186</v>
+      </c>
+      <c r="D2" s="2">
+        <v>20885064669</v>
+      </c>
+      <c r="E2" s="2">
+        <v>6955169151</v>
+      </c>
+      <c r="F2" s="2">
+        <v>27840233820</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
-        <v>462472582.30000001</v>
-      </c>
-      <c r="C3" s="3">
-        <v>621054701</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1062501318</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2546000000</v>
-      </c>
-      <c r="F3" s="3">
-        <v>3658501318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
+        <v>322535647</v>
+      </c>
+      <c r="C3" s="2">
+        <v>553817246</v>
+      </c>
+      <c r="D3" s="2">
+        <v>876352893</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1654000000</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2530352893</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
-        <v>318861189.19999999</v>
-      </c>
-      <c r="C4" s="3">
-        <v>22812946.48</v>
-      </c>
-      <c r="D4" s="3">
-        <v>341674135.69999999</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="B4" s="2">
+        <v>12966620741</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6469110079</v>
+      </c>
+      <c r="D4" s="2">
+        <v>19435730820</v>
+      </c>
+      <c r="E4" s="2">
         <v>6025500000</v>
       </c>
-      <c r="F4" s="3">
-        <v>6365174136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="2">
+        <v>22402587909</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
-        <v>185899318.19999999</v>
-      </c>
-      <c r="C5" s="3">
-        <v>32427354.550000001</v>
-      </c>
-      <c r="D5" s="3">
-        <v>228326672.80000001</v>
-      </c>
-      <c r="E5" s="3">
-        <v>263320000000</v>
-      </c>
-      <c r="F5" s="3">
-        <v>266713266673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
-        <v>269336206.80000001</v>
-      </c>
-      <c r="C6" s="3">
-        <v>77971382.079999998</v>
-      </c>
-      <c r="D6" s="3">
-        <v>261088351.69999999</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>261088351.69999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>86493115</v>
+      </c>
+      <c r="C6" s="2">
+        <v>188000000</v>
+      </c>
+      <c r="D6" s="2">
+        <v>274493115</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3862183355</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4136676470</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
-        <v>573367392.20000005</v>
-      </c>
-      <c r="C7" s="3">
-        <v>18339716.079999998</v>
-      </c>
-      <c r="D7" s="3">
-        <v>611057108.29999995</v>
-      </c>
-      <c r="E7" s="3">
-        <v>3065000000</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3688707108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>181740040</v>
+      </c>
+      <c r="C7" s="2">
+        <v>18850000</v>
+      </c>
+      <c r="D7" s="2">
+        <v>200590040</v>
+      </c>
+      <c r="E7" s="2">
+        <v>739212185</v>
+      </c>
+      <c r="F7" s="2">
+        <v>939802225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
-        <v>110066559.5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>11384103.65</v>
-      </c>
-      <c r="D8" s="3">
-        <v>113450663.09999999</v>
-      </c>
-      <c r="E8" s="3">
-        <v>10111000000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>10224450663</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>65770965</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="D8" s="2">
+        <v>71770965</v>
+      </c>
+      <c r="E8" s="2">
+        <v>270955789</v>
+      </c>
+      <c r="F8" s="2">
+        <v>342726754</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
-        <v>101311864</v>
-      </c>
-      <c r="C9" s="3">
-        <v>12984967.33</v>
-      </c>
-      <c r="D9" s="3">
-        <v>107296831.3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>379000000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>486296831.30000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
-        <v>677308192.60000002</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>677308192.60000002</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>677308192.60000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>24957623</v>
+      </c>
+      <c r="C10" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="D10" s="2">
+        <v>30957623</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1560619000</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1591576623</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
-        <v>488275684.10000002</v>
-      </c>
-      <c r="C11" s="3">
-        <v>16705378.6</v>
-      </c>
-      <c r="D11" s="3">
-        <v>413892105.19999999</v>
-      </c>
-      <c r="E11" s="3">
-        <v>13846833333</v>
-      </c>
-      <c r="F11" s="3">
-        <v>18285743337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>152965425</v>
+      </c>
+      <c r="C11" s="2">
+        <v>19499035</v>
+      </c>
+      <c r="D11" s="2">
+        <v>172464460</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3872782174</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4045246634</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
-        <v>20572200</v>
-      </c>
-      <c r="C12" s="3">
-        <v>17227600</v>
-      </c>
-      <c r="D12" s="3">
-        <v>39799800</v>
-      </c>
-      <c r="E12" s="3">
-        <v>915000000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>936799800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3">
-        <v>1519128693</v>
-      </c>
-      <c r="C13" s="3">
-        <v>3045100261</v>
-      </c>
-      <c r="D13" s="3">
-        <v>4604228954</v>
-      </c>
-      <c r="E13" s="3">
-        <v>5858000000</v>
-      </c>
-      <c r="F13" s="3">
-        <v>10462228954</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>741452420</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1517900000</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2259352420</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3500000000</v>
+      </c>
+      <c r="F13" s="2">
+        <v>5759352420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
-        <v>67113487.5</v>
-      </c>
-      <c r="C14" s="3">
-        <v>16910052.690000001</v>
-      </c>
-      <c r="D14" s="3">
-        <v>88023540.189999998</v>
-      </c>
-      <c r="E14" s="3">
-        <v>165000000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>253523540.19999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>41475000</v>
+      </c>
+      <c r="C14" s="2">
+        <v>15671037</v>
+      </c>
+      <c r="D14" s="2">
+        <v>57146037</v>
+      </c>
+      <c r="E14" s="2">
+        <v>308669723</v>
+      </c>
+      <c r="F14" s="2">
+        <v>365815760</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3">
-        <v>5683750263</v>
-      </c>
-      <c r="C15" s="3">
-        <v>71849237.680000007</v>
-      </c>
-      <c r="D15" s="3">
-        <v>5862263617</v>
-      </c>
-      <c r="E15" s="3">
-        <v>7785600000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>13657863617</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>1663271635</v>
+      </c>
+      <c r="C15" s="2">
+        <v>189200000</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1852471635</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2815000000</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4667471635</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3">
-        <v>525015287.39999998</v>
-      </c>
-      <c r="C16" s="3">
-        <v>89712371.739999995</v>
-      </c>
-      <c r="D16" s="3">
-        <v>634727659.10000002</v>
-      </c>
-      <c r="E16" s="3">
-        <v>679000000</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1313727659</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>173974394</v>
+      </c>
+      <c r="C16" s="2">
+        <v>635306010</v>
+      </c>
+      <c r="D16" s="2">
+        <v>809280404</v>
+      </c>
+      <c r="E16" s="2">
+        <v>942618075</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1751898479</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3">
-        <v>273066530.19999999</v>
-      </c>
-      <c r="C17" s="3">
-        <v>17211374</v>
-      </c>
-      <c r="D17" s="3">
-        <v>292277904.19999999</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5243118000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5515395904</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>460000000</v>
+      </c>
+      <c r="C17" s="2">
+        <v>14400000</v>
+      </c>
+      <c r="D17" s="2">
+        <v>474400000</v>
+      </c>
+      <c r="E17" s="2">
+        <v>654104400</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1128504400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3">
-        <v>1026410186</v>
-      </c>
-      <c r="C18" s="3">
-        <v>275920722.10000002</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1302330908</v>
-      </c>
-      <c r="E18" s="3">
-        <v>846000000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2148330908</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="3">
-        <v>201583990</v>
-      </c>
-      <c r="C19" s="3">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>201583990</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>201583990</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>68623400</v>
+      </c>
+      <c r="C19" s="2">
+        <v>13300000</v>
+      </c>
+      <c r="D19" s="2">
+        <v>81923400</v>
+      </c>
+      <c r="E19" s="2">
+        <v>726000000</v>
+      </c>
+      <c r="F19" s="2">
+        <v>807923400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="3">
-        <v>6976500</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
-        <v>6976500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>6976500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>61656822</v>
+      </c>
+      <c r="C20" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="D20" s="2">
+        <v>79656822</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3702203846</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3781860668</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="3">
-        <v>6910350</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <v>6910350</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>6910350</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>124776892</v>
+      </c>
+      <c r="C21" s="2">
+        <v>18500000</v>
+      </c>
+      <c r="D21" s="2">
+        <v>143276892</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1785948639</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1929225531</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3">
-        <v>131779993.09999999</v>
-      </c>
-      <c r="C22" s="3">
-        <v>13107400</v>
-      </c>
-      <c r="D22" s="3">
-        <v>140887393.09999999</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2601500000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2752387393</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>128480231</v>
+      </c>
+      <c r="C22" s="2">
+        <v>17443841</v>
+      </c>
+      <c r="D22" s="2">
+        <v>145924072</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2496000000</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2641924072</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3">
-        <v>110446652.8</v>
-      </c>
-      <c r="C23" s="3">
-        <v>9351322</v>
-      </c>
-      <c r="D23" s="3">
-        <v>120197974.8</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2570600000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2902226775</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>25606744</v>
+      </c>
+      <c r="C23" s="2">
+        <v>161500000</v>
+      </c>
+      <c r="D23" s="2">
+        <v>187106744</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1165550000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1352656744</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3">
-        <v>134600177.30000001</v>
-      </c>
-      <c r="C24" s="3">
-        <v>11860000</v>
-      </c>
-      <c r="D24" s="3">
-        <v>148460177.30000001</v>
-      </c>
-      <c r="E24" s="3">
-        <v>9995000000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>10199650177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>371267762</v>
+      </c>
+      <c r="C24" s="2">
+        <v>48285600</v>
+      </c>
+      <c r="D24" s="2">
+        <v>419553362</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2278707129</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2698260491</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
-        <v>270883462.60000002</v>
-      </c>
-      <c r="C25" s="3">
-        <v>19656250</v>
-      </c>
-      <c r="D25" s="3">
-        <v>292539712.60000002</v>
-      </c>
-      <c r="E25" s="3">
-        <v>527000000</v>
-      </c>
-      <c r="F25" s="3">
-        <v>819093412.60000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>5685260024</v>
+      </c>
+      <c r="C25" s="2">
+        <v>362934954</v>
+      </c>
+      <c r="D25" s="2">
+        <v>6048194978</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3238402223</v>
+      </c>
+      <c r="F25" s="2">
+        <v>9286597201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
-        <v>178035997.80000001</v>
-      </c>
-      <c r="C26" s="3">
-        <v>57476821.460000001</v>
-      </c>
-      <c r="D26" s="3">
-        <v>239512819.30000001</v>
-      </c>
-      <c r="E26" s="3">
-        <v>3411000000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>580612819.29999995</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>95870753</v>
+      </c>
+      <c r="C26" s="2">
+        <v>39326100</v>
+      </c>
+      <c r="D26" s="2">
+        <v>135196853</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2008750000</v>
+      </c>
+      <c r="F26" s="2">
+        <v>2143946853</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3">
-        <v>241024782.19999999</v>
-      </c>
-      <c r="C27" s="3">
-        <v>11860000</v>
-      </c>
-      <c r="D27" s="3">
-        <v>254884782.19999999</v>
-      </c>
-      <c r="E27" s="3">
-        <v>3279700000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>3554814782</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>2557449656</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1198709563</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3756159219</v>
+      </c>
+      <c r="E27" s="2">
+        <v>5885260000</v>
+      </c>
+      <c r="F27" s="2">
+        <v>9641419219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="3">
-        <v>608826114.29999995</v>
-      </c>
-      <c r="C28" s="3">
-        <v>66476821.460000001</v>
-      </c>
-      <c r="D28" s="3">
-        <v>626970954.29999995</v>
-      </c>
-      <c r="E28" s="3">
-        <v>2676000000</v>
-      </c>
-      <c r="F28" s="3">
-        <v>894570954.29999995</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>175352525</v>
+      </c>
+      <c r="C28" s="2">
+        <v>225000000</v>
+      </c>
+      <c r="D28" s="2">
+        <v>400352525</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1508480666</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1908833191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="3">
-        <v>312935929.10000002</v>
-      </c>
-      <c r="C29" s="3">
-        <v>797764026.20000005</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1130699955</v>
-      </c>
-      <c r="E29" s="3">
-        <v>36374500000</v>
-      </c>
-      <c r="F29" s="3">
-        <v>47781499955</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>177003112</v>
+      </c>
+      <c r="C29" s="2">
+        <v>10500000</v>
+      </c>
+      <c r="D29" s="2">
+        <v>187503112</v>
+      </c>
+      <c r="E29" s="2">
+        <v>95200000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>282703112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="3">
-        <v>147732064.19999999</v>
-      </c>
-      <c r="C30" s="3">
-        <v>15822177.1</v>
-      </c>
-      <c r="D30" s="3">
-        <v>161554241.30000001</v>
-      </c>
-      <c r="E30" s="3">
-        <v>3204000000</v>
-      </c>
-      <c r="F30" s="3">
-        <v>471954241.30000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>64716174</v>
+      </c>
+      <c r="C30" s="2">
+        <v>13000000</v>
+      </c>
+      <c r="D30" s="2">
+        <v>77716174</v>
+      </c>
+      <c r="E30" s="2">
+        <v>58053025</v>
+      </c>
+      <c r="F30" s="2">
+        <v>135769199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="3">
-        <v>518449487.80000001</v>
-      </c>
-      <c r="C31" s="3">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3">
-        <v>518449487.80000001</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
-        <v>518449487.80000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>25480255</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>25480255</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>25480255</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="3">
-        <v>258238168.19999999</v>
-      </c>
-      <c r="C32" s="3">
-        <v>18182554</v>
-      </c>
-      <c r="D32" s="3">
-        <v>278420722.19999999</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1669000000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>445320722.19999999</v>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>60200000</v>
+      </c>
+      <c r="D32" s="2">
+        <v>60200000</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>60200000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="2">
+        <v>85658342</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1512000000</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1597658342</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1988634858</v>
+      </c>
+      <c r="F33" s="2">
+        <v>3586293200</v>
       </c>
     </row>
   </sheetData>
